--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_293_R30.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_293_R30.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8385</v>
+        <v>4.2637</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1903</v>
+        <v>3.7499</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6482</v>
+        <v>0.5138</v>
       </c>
       <c r="G2" t="n">
         <v>-0.5669999999999999</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7071</v>
+        <v>1.1323</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6597</v>
+        <v>1.2193</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0475</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>2.5387</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2743</v>
+        <v>3.1866</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2324</v>
+        <v>2.2456</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0419</v>
+        <v>0.9411</v>
       </c>
       <c r="G3" t="n">
         <v>-1.9888</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1187</v>
+        <v>1.031</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7343</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3844</v>
+        <v>0.2836</v>
       </c>
       <c r="V3" t="n">
         <v>3.2166</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>Z. HANKINS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7647</v>
+        <v>1.1462</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4494</v>
+        <v>2.6835</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.6847</v>
+        <v>-1.5373</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.5062</v>
+        <v>0.7873</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7369</v>
+        <v>0.2486</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2308</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.137</v>
+        <v>1.842</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6855</v>
+        <v>1.1427</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5486</v>
+        <v>0.6993</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3692</v>
+        <v>-1.0547</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0514</v>
+        <v>-0.8942</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3178</v>
+        <v>-0.1605</v>
       </c>
       <c r="P4" t="n">
         <v>0.4639</v>
@@ -766,28 +766,28 @@
         <v>0.4639</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2013</v>
+        <v>0.9671</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8363</v>
+        <v>0.8415</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3651</v>
+        <v>0.1256</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3943</v>
+        <v>-1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Z. HANKINS</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5085</v>
+        <v>-0.1303</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1803</v>
+        <v>2.6551</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6718</v>
+        <v>-2.7855</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7873</v>
+        <v>-1.5062</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2486</v>
+        <v>-1.7369</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.2308</v>
       </c>
       <c r="J5" t="n">
-        <v>1.842</v>
+        <v>-0.137</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1427</v>
+        <v>-0.6855</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6993</v>
+        <v>0.5486</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0547</v>
+        <v>-1.3692</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8942</v>
+        <v>-1.0514</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1605</v>
+        <v>-0.3178</v>
       </c>
       <c r="P5" t="n">
         <v>0.4639</v>
@@ -844,28 +844,28 @@
         <v>0.4639</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3295</v>
+        <v>1.3063</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3383</v>
+        <v>1.042</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.2642</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. DIBARTOLOMEO</t>
+          <t>J. CLARK III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1193</v>
+        <v>-1.4415</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2587</v>
+        <v>-0.9436</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8606</v>
+        <v>-0.4979</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2035</v>
+        <v>-1.4956</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.15</v>
+        <v>2.0179</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0535</v>
+        <v>-3.5134</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0504</v>
+        <v>0.0665</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0504</v>
+        <v>2.9444</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-2.8778</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2539</v>
+        <v>-1.5621</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2004</v>
+        <v>-0.9265</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0535</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.756</v>
+        <v>-0.1779</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1494</v>
+        <v>0.1496</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6067</v>
+        <v>-0.3275</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>T. BLATT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4896</v>
+        <v>-1.5285</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8182</v>
+        <v>-1.3587</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6714</v>
+        <v>-0.1697</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2114</v>
+        <v>-3.8843</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-1.1906</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2643</v>
+        <v>-2.6937</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7359</v>
+        <v>-2.5649</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7359</v>
+        <v>0.3865</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-2.9514</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4755</v>
+        <v>-1.3194</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2112</v>
+        <v>-1.5771</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2643</v>
+        <v>0.2578</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8839</v>
+        <v>0.3558</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.224</v>
+        <v>0.134</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6598000000000001</v>
+        <v>0.2219</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3943</v>
+        <v>1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CLARK III</t>
+          <t>J. DIBARTOLOMEO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.625</v>
+        <v>-1.9363</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7574</v>
+        <v>-1.1093</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8676</v>
+        <v>-0.827</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4956</v>
+        <v>-0.2035</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0179</v>
+        <v>-0.15</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.5134</v>
+        <v>-0.0535</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0665</v>
+        <v>0.0504</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9444</v>
+        <v>0.0504</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.8778</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5621</v>
+        <v>-0.2539</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9265</v>
+        <v>-0.2004</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.0535</v>
       </c>
       <c r="P8" t="n">
-        <v>0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3614</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6972</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. BLATT</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6408</v>
+        <v>-2.5493</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5383</v>
+        <v>-0.7435</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1025</v>
+        <v>-1.8058</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.8843</v>
+        <v>-1.2114</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1906</v>
+        <v>-0.9471000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6937</v>
+        <v>-0.2643</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5649</v>
+        <v>-0.7359</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3865</v>
+        <v>-0.7359</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.9514</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3194</v>
+        <v>-0.4755</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5771</v>
+        <v>-0.2112</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2578</v>
+        <v>-0.2643</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7565</v>
+        <v>-0.9436</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0455</v>
+        <v>-0.1494</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2891</v>
+        <v>-0.7943</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>L. WALKER IV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4712</v>
+        <v>-2.6223</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7193</v>
+        <v>-0.6377</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7519</v>
+        <v>-1.9846</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.6794</v>
+        <v>-2.1581</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.7192</v>
+        <v>-1.3181</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-0.84</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6132</v>
+        <v>0.6052</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9741</v>
+        <v>0.6491</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6391</v>
+        <v>-0.0438</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0663</v>
+        <v>-2.7633</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7452</v>
+        <v>-1.9671</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3211</v>
+        <v>-0.7961</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.7834</v>
+        <v>-0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.639</v>
+        <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>2.3138</v>
+        <v>0.3038</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2467</v>
+        <v>0.0044</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0671</v>
+        <v>0.2994</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2862</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
         <v>-1.6083</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. WALKER IV</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2805</v>
+        <v>-4.5081</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1278</v>
+        <v>-3.5882</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1527</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1581</v>
+        <v>-3.6794</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3181</v>
+        <v>-2.7192</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.84</v>
+        <v>-0.9602000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6052</v>
+        <v>-1.6132</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6491</v>
+        <v>-0.9741</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0438</v>
+        <v>-0.6391</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.7633</v>
+        <v>-2.0663</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9671</v>
+        <v>-1.7452</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7961</v>
+        <v>-0.3211</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.232</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3195</v>
+        <v>-4.639</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3544</v>
+        <v>1.2768</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4857</v>
+        <v>0.3778</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1314</v>
+        <v>0.899</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5361</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0722</v>
+        <v>2.2862</v>
       </c>
       <c r="X11" t="n">
         <v>-1.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.240400000000001</v>
+        <v>-6.119799999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1.832699999999998</v>
+        <v>2.9531</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.0731</v>
+        <v>-9.072799999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-15.907</v>
@@ -1381,7 +1381,7 @@
         <v>-1.8891</v>
       </c>
       <c r="P12" t="n">
-        <v>1.942890293094024e-16</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>-11.5977</v>
@@ -1390,13 +1390,13 @@
         <v>11.5976</v>
       </c>
       <c r="S12" t="n">
-        <v>3.558200000000001</v>
+        <v>4.6785</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2465</v>
+        <v>4.3667</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3120999999999996</v>
+        <v>0.3118000000000002</v>
       </c>
       <c r="V12" t="n">
         <v>5.1085</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.5816</v>
+        <v>4.1155</v>
       </c>
       <c r="E13" t="n">
-        <v>5.276</v>
+        <v>4.6863</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6945</v>
+        <v>-0.5708</v>
       </c>
       <c r="G13" t="n">
         <v>3.7512</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1876</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9243</v>
+        <v>0.3345</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1119</v>
+        <v>-0.9882</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1418</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0098</v>
+        <v>3.748</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7638</v>
+        <v>3.1177</v>
       </c>
       <c r="F14" t="n">
-        <v>1.246</v>
+        <v>0.6303</v>
       </c>
       <c r="G14" t="n">
         <v>3.937</v>
@@ -1546,13 +1546,13 @@
         <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5355</v>
+        <v>-0.7973</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7389</v>
+        <v>-0.3851</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2034</v>
+        <v>-0.4123</v>
       </c>
       <c r="V14" t="n">
         <v>1.0722</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1892</v>
+        <v>2.3065</v>
       </c>
       <c r="E15" t="n">
-        <v>3.141</v>
+        <v>3.0231</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9518</v>
+        <v>-0.7166</v>
       </c>
       <c r="G15" t="n">
         <v>1.617</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7473</v>
+        <v>-0.63</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4446</v>
+        <v>0.3266</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1918</v>
+        <v>-0.9566</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5361</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0252</v>
+        <v>1.3905</v>
       </c>
       <c r="E16" t="n">
-        <v>1.847</v>
+        <v>1.7017</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8218</v>
+        <v>-0.3112</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1988</v>
+        <v>3.3372</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4369</v>
+        <v>2.0924</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6357</v>
+        <v>1.2448</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5493</v>
+        <v>2.6512</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1211</v>
+        <v>2.5039</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4282</v>
+        <v>0.1472</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3505</v>
+        <v>0.6861</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5581</v>
+        <v>-0.4116</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2075</v>
+        <v>1.0976</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4167</v>
+        <v>-0.3205</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2977</v>
+        <v>-0.4676</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1191</v>
+        <v>0.1472</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.7501</v>
+        <v>-0.9304</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7501</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5433</v>
+        <v>0.62</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3478</v>
+        <v>1.1393</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8045</v>
+        <v>-0.5194</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3372</v>
+        <v>0.1988</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0924</v>
+        <v>-0.4369</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2448</v>
+        <v>0.6357</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6512</v>
+        <v>0.5493</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5039</v>
+        <v>0.1211</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1472</v>
+        <v>0.4282</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6861</v>
+        <v>-0.3505</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4116</v>
+        <v>-0.5581</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0976</v>
+        <v>0.2075</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1677</v>
+        <v>1.0115</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8215</v>
+        <v>0.59</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3462</v>
+        <v>0.4215</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9304</v>
+        <v>-1.7501</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6083</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5085</v>
+        <v>0.4292</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9043</v>
+        <v>0.4325</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3958</v>
+        <v>-0.0033</v>
       </c>
       <c r="G18" t="n">
         <v>3.5832</v>
@@ -1858,13 +1858,13 @@
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2913</v>
+        <v>-0.3705</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4015</v>
+        <v>-0.0703</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6928</v>
+        <v>-0.3002</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. RANDOLPH</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7701</v>
+        <v>-0.5298</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4465</v>
+        <v>-1.6124</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2166</v>
+        <v>1.0826</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1528</v>
+        <v>-0.0497</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8812</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0339</v>
+        <v>0.5385</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4386</v>
+        <v>-0.0495</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7023</v>
+        <v>0.1918</v>
       </c>
       <c r="L19" t="n">
-        <v>1.141</v>
+        <v>-0.2413</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2859</v>
+        <v>-0.0002</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1788</v>
+        <v>-0.78</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.107</v>
+        <v>0.7798</v>
       </c>
       <c r="P19" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3145</v>
+        <v>-0.4079</v>
       </c>
       <c r="T19" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.9392</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3224</v>
+        <v>0.5313</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X19" t="n">
         <v>-1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. EDWARDS</t>
+          <t>L. RANDOLPH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2606</v>
+        <v>-0.6521</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6072</v>
+        <v>0.5645</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6534</v>
+        <v>-1.2166</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1254</v>
+        <v>0.1528</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4166</v>
+        <v>-0.8812</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.542</v>
+        <v>1.0339</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6151</v>
+        <v>0.4386</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1344</v>
+        <v>-0.7023</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7495000000000001</v>
+        <v>1.141</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4897</v>
+        <v>-0.2859</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2822</v>
+        <v>-0.1788</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2075</v>
+        <v>-0.107</v>
       </c>
       <c r="P20" t="n">
         <v>0.4639</v>
@@ -2014,28 +2014,28 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9212</v>
+        <v>-0.1966</v>
       </c>
       <c r="T20" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.1259</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9291</v>
+        <v>-0.3224</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>K. EDWARDS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3269</v>
+        <v>-1.109</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0842</v>
+        <v>-0.4892</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7573</v>
+        <v>-0.6198</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0497</v>
+        <v>-0.1254</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5881999999999999</v>
+        <v>0.4166</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5385</v>
+        <v>-0.542</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0495</v>
+        <v>-0.6151</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1918</v>
+        <v>0.1344</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2413</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0002</v>
+        <v>0.4897</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.78</v>
+        <v>0.2822</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7798</v>
+        <v>0.2075</v>
       </c>
       <c r="P21" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.205</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.411</v>
+        <v>0.1259</v>
       </c>
       <c r="U21" t="n">
-        <v>0.206</v>
+        <v>-0.8955</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5361</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2599</v>
+        <v>-2.2922</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9624</v>
+        <v>-3.4906</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7024</v>
+        <v>1.1983</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4951</v>
@@ -2170,13 +2170,13 @@
         <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3949</v>
+        <v>0.3626</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4244</v>
+        <v>0.0474</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8193</v>
+        <v>0.3152</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5361</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.2401</v>
+        <v>8.026600000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>9.0726</v>
+        <v>9.072899999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8327</v>
+        <v>-1.0465</v>
       </c>
       <c r="G23" t="n">
         <v>15.907</v>
       </c>
       <c r="H23" t="n">
-        <v>6.721800000000001</v>
+        <v>6.7218</v>
       </c>
       <c r="I23" t="n">
         <v>9.184699999999999</v>
@@ -2227,19 +2227,19 @@
         <v>12.5179</v>
       </c>
       <c r="L23" t="n">
-        <v>1.8893</v>
+        <v>1.889299999999999</v>
       </c>
       <c r="M23" t="n">
         <v>1.4996</v>
       </c>
       <c r="N23" t="n">
-        <v>-5.796200000000002</v>
+        <v>-5.796200000000001</v>
       </c>
       <c r="O23" t="n">
         <v>7.295699999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>-11.5977</v>
@@ -2248,19 +2248,19 @@
         <v>11.5977</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.5585</v>
+        <v>-2.7721</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3118999999999997</v>
+        <v>-0.3119000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.2464</v>
+        <v>-2.46</v>
       </c>
       <c r="V23" t="n">
         <v>-5.1085</v>
       </c>
       <c r="W23" t="n">
-        <v>6.575000000000001</v>
+        <v>6.575</v>
       </c>
       <c r="X23" t="n">
         <v>-11.6835</v>
